--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487772_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487772_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. LAFUENTE VELAZQUEZ</t>
+          <t>L. GARCIA MUÑOZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.401</v>
+        <v>11.5635</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7281</v>
+        <v>8.0633</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6728</v>
+        <v>3.5002</v>
       </c>
       <c r="G2" t="n">
-        <v>7.0598</v>
+        <v>7.8184</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1067</v>
+        <v>4.9233</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9531</v>
+        <v>2.895</v>
       </c>
       <c r="J2" t="n">
-        <v>6.5048</v>
+        <v>6.5286</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1639</v>
+        <v>4.0295</v>
       </c>
       <c r="L2" t="n">
-        <v>4.3409</v>
+        <v>2.4991</v>
       </c>
       <c r="M2" t="n">
-        <v>0.555</v>
+        <v>1.2898</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9428</v>
+        <v>0.8938</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3878</v>
+        <v>0.396</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q2" t="n">
         <v>-2.2893</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1218</v>
+        <v>2.4974</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5087</v>
+        <v>-0.1955</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2827</v>
+        <v>0.0915</v>
       </c>
       <c r="U2" t="n">
-        <v>1.226</v>
+        <v>-0.287</v>
       </c>
       <c r="V2" t="n">
+        <v>3.7325</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.7325</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-0.23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>J. LAFUENTE VELAZQUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>10.7341</v>
+        <v>9.809699999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>7.5275</v>
+        <v>5.8709</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2066</v>
+        <v>3.9388</v>
       </c>
       <c r="G3" t="n">
-        <v>7.8184</v>
+        <v>7.0598</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9233</v>
+        <v>3.1067</v>
       </c>
       <c r="I3" t="n">
-        <v>2.895</v>
+        <v>3.9531</v>
       </c>
       <c r="J3" t="n">
-        <v>6.5286</v>
+        <v>6.5048</v>
       </c>
       <c r="K3" t="n">
-        <v>4.0295</v>
+        <v>2.1639</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4991</v>
+        <v>4.3409</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2898</v>
+        <v>0.555</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8938</v>
+        <v>0.9428</v>
       </c>
       <c r="O3" t="n">
-        <v>0.396</v>
+        <v>-0.3878</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.2893</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4974</v>
+        <v>3.1218</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0249</v>
+        <v>1.9175</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4443</v>
+        <v>1.4254</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5806</v>
+        <v>0.492</v>
       </c>
       <c r="V3" t="n">
-        <v>3.7325</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.7325</v>
+        <v>0.23</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.8984</v>
+        <v>7.1271</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1241</v>
+        <v>5.0885</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7744</v>
+        <v>2.0386</v>
       </c>
       <c r="G4" t="n">
         <v>6.734</v>
@@ -766,13 +766,13 @@
         <v>3.1218</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3955</v>
+        <v>-0.1668</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7177</v>
+        <v>0.2467</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6778</v>
+        <v>-0.4136</v>
       </c>
       <c r="V4" t="n">
         <v>-1.5213</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7638</v>
+        <v>3.3763</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4912</v>
+        <v>0.6339</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2727</v>
+        <v>2.7424</v>
       </c>
       <c r="G5" t="n">
         <v>2.5841</v>
@@ -844,13 +844,13 @@
         <v>2.2893</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1828</v>
+        <v>0.7953</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8293</v>
+        <v>0.972</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6465</v>
+        <v>-0.1767</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0437</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0299</v>
+        <v>2.776</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0233</v>
+        <v>2.9161</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0066</v>
+        <v>-0.1401</v>
       </c>
       <c r="G6" t="n">
         <v>2.6552</v>
@@ -922,13 +922,13 @@
         <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5017</v>
+        <v>0.2478</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1924</v>
+        <v>0.0853</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3093</v>
+        <v>0.1625</v>
       </c>
       <c r="V6" t="n">
         <v>-1.1675</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5614</v>
+        <v>2.7551</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4731</v>
+        <v>0.9016999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0883</v>
+        <v>1.8534</v>
       </c>
       <c r="G7" t="n">
         <v>0.8786</v>
@@ -1000,13 +1000,13 @@
         <v>2.9137</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6016</v>
+        <v>0.7953</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2048</v>
+        <v>0.6334</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3967</v>
+        <v>0.1619</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5838</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8137</v>
+        <v>1.8328</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6015</v>
+        <v>1.7086</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2123</v>
+        <v>0.1242</v>
       </c>
       <c r="G8" t="n">
         <v>1.7297</v>
@@ -1078,13 +1078,13 @@
         <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2916</v>
+        <v>-0.2725</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4567</v>
+        <v>-0.3495</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1651</v>
+        <v>0.077</v>
       </c>
       <c r="V8" t="n">
         <v>0.5838</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2993</v>
+        <v>-0.4508</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1934</v>
+        <v>-0.5567</v>
       </c>
       <c r="F9" t="n">
         <v>0.1058</v>
@@ -1156,10 +1156,10 @@
         <v>0.6244</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1678</v>
+        <v>0.4177</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1025</v>
+        <v>0.3524</v>
       </c>
       <c r="U9" t="n">
         <v>0.06519999999999999</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.023</v>
+        <v>-1.4373</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9042</v>
+        <v>-0.5828</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1188</v>
+        <v>-0.8545</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7919</v>
@@ -1234,13 +1234,13 @@
         <v>1.8731</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0176</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2048</v>
+        <v>0.5263</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1872</v>
+        <v>0.077</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2764</v>
+        <v>-2.0914</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7786</v>
+        <v>-1.5643</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4978</v>
+        <v>-0.5272</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3467</v>
@@ -1312,13 +1312,13 @@
         <v>0.4162</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3053</v>
+        <v>-0.1204</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3262</v>
+        <v>-0.1119</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0209</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0218</v>
+        <v>-4.0805</v>
       </c>
       <c r="E12" t="n">
         <v>-3.2452</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7766</v>
+        <v>-0.8353</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4366</v>
@@ -1390,13 +1390,13 @@
         <v>1.0406</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7281</v>
+        <v>0.6694</v>
       </c>
       <c r="T12" t="n">
         <v>0.2577</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4704</v>
+        <v>0.4117</v>
       </c>
       <c r="V12" t="n">
         <v>-2.1051</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>31.18039999999999</v>
+        <v>31.18049999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>19.2342</v>
+        <v>19.234</v>
       </c>
       <c r="F13" t="n">
         <v>11.9463</v>
@@ -1468,13 +1468,13 @@
         <v>19.7714</v>
       </c>
       <c r="S13" t="n">
-        <v>4.691000000000001</v>
+        <v>4.6911</v>
       </c>
       <c r="T13" t="n">
         <v>4.1293</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5614999999999999</v>
+        <v>0.5615</v>
       </c>
       <c r="V13" t="n">
         <v>-2.105100000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4887</v>
+        <v>3.5133</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7305</v>
+        <v>4.3735</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2418</v>
+        <v>-0.8602</v>
       </c>
       <c r="G14" t="n">
         <v>4.4124</v>
@@ -1546,13 +1546,13 @@
         <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.802</v>
+        <v>-0.7773</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9134</v>
+        <v>-0.2705</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8885</v>
+        <v>-0.5069</v>
       </c>
       <c r="V14" t="n">
         <v>1.7513</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>J. KNOTEK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.004</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.5317</v>
+        <v>1.03</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5276999999999999</v>
+        <v>-1.61</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8597</v>
+        <v>-2.4283</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0277</v>
+        <v>-3.7975</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8875</v>
+        <v>1.3691</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8759</v>
+        <v>0.1111</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5137</v>
+        <v>-1.6826</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3896</v>
+        <v>1.7937</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0162</v>
+        <v>-2.5394</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4859</v>
+        <v>-2.1148</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5021</v>
+        <v>-0.4245</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0812</v>
+        <v>-0.2081</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8325</v>
+        <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5206</v>
+        <v>-0.0467</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8416</v>
+        <v>-0.2705</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3209</v>
+        <v>0.2238</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5838</v>
+        <v>0.23</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5838</v>
+        <v>1.3975</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.0223</v>
+        <v>-0.6739000000000001</v>
       </c>
       <c r="E16" t="n">
         <v>1.3456</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3678</v>
+        <v>-2.0194</v>
       </c>
       <c r="G16" t="n">
         <v>1.0707</v>
@@ -1702,13 +1702,13 @@
         <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9036</v>
+        <v>-0.5552</v>
       </c>
       <c r="T16" t="n">
         <v>0.0619</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9655</v>
+        <v>-0.6171</v>
       </c>
       <c r="V16" t="n">
         <v>-1.3975</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0391</v>
+        <v>-1.1962</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2203</v>
+        <v>0.3274</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2594</v>
+        <v>-1.5236</v>
       </c>
       <c r="G17" t="n">
         <v>-1.7819</v>
@@ -1780,13 +1780,13 @@
         <v>0.6244</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5891</v>
+        <v>-0.7462</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3915</v>
+        <v>-0.2843</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1976</v>
+        <v>-0.4619</v>
       </c>
       <c r="V17" t="n">
         <v>0.7076</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. KNOTEK</t>
+          <t>P. ELSO GONZALEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.223</v>
+        <v>-1.661</v>
       </c>
       <c r="E18" t="n">
-        <v>0.387</v>
+        <v>-1.1501</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.61</v>
+        <v>-0.5109</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4283</v>
+        <v>0.4714</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.7975</v>
+        <v>0.3008</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3691</v>
+        <v>0.1706</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1111</v>
+        <v>1.1858</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.6826</v>
+        <v>0.0192</v>
       </c>
       <c r="L18" t="n">
-        <v>1.7937</v>
+        <v>1.1667</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5394</v>
+        <v>-0.7144</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1148</v>
+        <v>0.2816</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4245</v>
+        <v>-0.996</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6649</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2081</v>
+        <v>-2.2893</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8731</v>
+        <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6896</v>
+        <v>-0.4674</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9134</v>
+        <v>-0.0467</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2238</v>
+        <v>-0.4208</v>
       </c>
       <c r="V18" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ELSO GONZALEZ</t>
+          <t>N. DEL VAL GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0514</v>
+        <v>-1.739</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3644</v>
+        <v>-2.1747</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6870000000000001</v>
+        <v>0.4357</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4714</v>
+        <v>-0.8597</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3008</v>
+        <v>0.0277</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1706</v>
+        <v>-0.8875</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1858</v>
+        <v>-0.8759</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0192</v>
+        <v>0.5137</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1667</v>
+        <v>-1.3896</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7144</v>
+        <v>0.0162</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2816</v>
+        <v>-0.4859</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.996</v>
+        <v>0.5021</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.6649</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2893</v>
+        <v>-2.0812</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8579</v>
+        <v>-0.2143</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.261</v>
+        <v>0.1986</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5969</v>
+        <v>-0.4129</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.826</v>
+        <v>-3.0402</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2125</v>
+        <v>-1.5695</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6136</v>
+        <v>-1.4707</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7544</v>
@@ -2014,13 +2014,13 @@
         <v>1.6649</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.9259</v>
+        <v>-1.1401</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1091</v>
+        <v>-0.4662</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8168</v>
+        <v>-0.6739000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>0.23</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.058</v>
+        <v>-5.1223</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4693</v>
+        <v>-4.0051</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5887</v>
+        <v>-1.1172</v>
       </c>
       <c r="G21" t="n">
         <v>-3.6368</v>
@@ -2092,13 +2092,13 @@
         <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1574</v>
+        <v>0.0931</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4501</v>
+        <v>-0.0857</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7073</v>
+        <v>0.1788</v>
       </c>
       <c r="V21" t="n">
         <v>1.7513</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2647</v>
+        <v>-5.349</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3157</v>
+        <v>-0.9702</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.5803</v>
+        <v>-4.3788</v>
       </c>
       <c r="G22" t="n">
         <v>-5.9032</v>
@@ -2170,13 +2170,13 @@
         <v>1.6649</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4522</v>
+        <v>0.3679</v>
       </c>
       <c r="T22" t="n">
-        <v>1.9441</v>
+        <v>0.6582</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4919</v>
+        <v>-0.2903</v>
       </c>
       <c r="V22" t="n">
         <v>-0.23</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.2199</v>
+        <v>-6.2936</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0221</v>
+        <v>-4.2721</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1977</v>
+        <v>-2.0216</v>
       </c>
       <c r="G23" t="n">
         <v>-3.0446</v>
@@ -2248,13 +2248,13 @@
         <v>0.8325</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0941</v>
+        <v>-0.1679</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7829</v>
+        <v>-0.0328</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3112</v>
+        <v>-0.135</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5838</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.9608</v>
+        <v>-8.324400000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3454</v>
+        <v>-4.8812</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.6154</v>
+        <v>-3.4432</v>
       </c>
       <c r="G24" t="n">
         <v>-8.9374</v>
@@ -2326,13 +2326,13 @@
         <v>2.2893</v>
       </c>
       <c r="S24" t="n">
-        <v>0.041</v>
+        <v>-0.3225</v>
       </c>
       <c r="T24" t="n">
-        <v>0.512</v>
+        <v>-0.0237</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.471</v>
+        <v>-0.2988</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9376</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-31.1805</v>
+        <v>-30.4664</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.9463</v>
+        <v>-11.9464</v>
       </c>
       <c r="F25" t="n">
-        <v>-19.234</v>
+        <v>-18.5199</v>
       </c>
       <c r="G25" t="n">
         <v>-23.3918</v>
@@ -2404,13 +2404,13 @@
         <v>14.5683</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.690999999999999</v>
+        <v>-3.976599999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5615999999999999</v>
+        <v>-0.5617000000000003</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.1292</v>
+        <v>-3.415</v>
       </c>
       <c r="V25" t="n">
         <v>2.1051</v>
